--- a/Sku_Scaner/barcode_data.xlsx
+++ b/Sku_Scaner/barcode_data.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27830"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28025"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\sku_Scaner\Sku_Scaner\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\sku_Scaner\Sku_Scaner\Sku_Scaner\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{020FEDAB-01AA-4776-ADC4-C91AA640B584}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6062546E-78CE-403D-8E86-A05302083032}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-75" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Resx Data" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="244" uniqueCount="239">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="247" uniqueCount="242">
   <si>
     <t>Name</t>
   </si>
@@ -737,6 +737,16 @@
   </si>
   <si>
     <t>8809800941290</t>
+  </si>
+  <si>
+    <t>20135R</t>
+  </si>
+  <si>
+    <t>21021R</t>
+  </si>
+  <si>
+    <t>8809800941429</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -779,8 +789,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
@@ -1083,7 +1094,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B122"/>
+  <dimension ref="A1:B124"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="8.75" bestFit="1" customWidth="1"/>
@@ -2067,6 +2078,19 @@
         <v>238</v>
       </c>
     </row>
+    <row r="123" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A123" t="s">
+        <v>239</v>
+      </c>
+      <c r="B123" s="1" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="124" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A124" t="s">
+        <v>240</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
